--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_EIFFAGE CB CIUDAD DE DOS HERMANAS.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_EIFFAGE CB CIUDAD DE DOS HERMANAS.xlsx
@@ -565,13 +565,13 @@
         <v>22</v>
       </c>
       <c r="D2" t="n">
-        <v>64.4131</v>
+        <v>54.7163</v>
       </c>
       <c r="E2" t="n">
-        <v>35.7287</v>
+        <v>29.4236</v>
       </c>
       <c r="F2" t="n">
-        <v>28.6841</v>
+        <v>25.2928</v>
       </c>
       <c r="G2" t="n">
         <v>24.2627</v>
@@ -610,13 +610,13 @@
         <v>52.4364</v>
       </c>
       <c r="S2" t="n">
-        <v>23.4216</v>
+        <v>13.7243</v>
       </c>
       <c r="T2" t="n">
-        <v>11.0059</v>
+        <v>4.7008</v>
       </c>
       <c r="U2" t="n">
-        <v>12.4157</v>
+        <v>9.0237</v>
       </c>
       <c r="V2" t="n">
         <v>26.1784</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. RAMOS RODRÍGUEZ</t>
+          <t>F. COTAN MOYA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>24.6357</v>
+        <v>39.2108</v>
       </c>
       <c r="E3" t="n">
-        <v>24.6357</v>
+        <v>23.0895</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>16.1208</v>
       </c>
       <c r="G3" t="n">
-        <v>24.6357</v>
+        <v>-12.0754</v>
       </c>
       <c r="H3" t="n">
-        <v>10.9505</v>
+        <v>-10.9997</v>
       </c>
       <c r="I3" t="n">
-        <v>13.6855</v>
+        <v>-1.075900000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>24.6357</v>
+        <v>19.9987</v>
       </c>
       <c r="K3" t="n">
-        <v>10.9505</v>
+        <v>3.1092</v>
       </c>
       <c r="L3" t="n">
-        <v>13.6855</v>
+        <v>16.8891</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>-32.0739</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>-14.1088</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>-17.9655</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>41.319</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-15.9345</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>57.2536</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.6582</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>-2.686</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>4.3442</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>8.3087</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>21.7116</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-13.4029</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>F. COTAN MOYA</t>
+          <t>M. RAMOS RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,70 +718,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>23.4402</v>
+        <v>24.6357</v>
       </c>
       <c r="E4" t="n">
-        <v>10.7306</v>
+        <v>24.6357</v>
       </c>
       <c r="F4" t="n">
-        <v>12.7098</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-12.0754</v>
+        <v>24.6357</v>
       </c>
       <c r="H4" t="n">
-        <v>-10.9997</v>
+        <v>10.9505</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.075900000000001</v>
+        <v>13.6855</v>
       </c>
       <c r="J4" t="n">
-        <v>19.9987</v>
+        <v>24.6357</v>
       </c>
       <c r="K4" t="n">
-        <v>3.1092</v>
+        <v>10.9505</v>
       </c>
       <c r="L4" t="n">
-        <v>16.8891</v>
+        <v>13.6855</v>
       </c>
       <c r="M4" t="n">
-        <v>-32.0739</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-14.1088</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-17.9655</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>41.319</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-15.9345</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>57.2536</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-14.112</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-15.0447</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9329000000000001</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>8.3087</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>21.7116</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-13.4029</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>23</v>
       </c>
       <c r="D5" t="n">
-        <v>19.0081</v>
+        <v>16.1503</v>
       </c>
       <c r="E5" t="n">
-        <v>9.736200000000002</v>
+        <v>6.377600000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>9.271699999999999</v>
+        <v>9.772600000000001</v>
       </c>
       <c r="G5" t="n">
         <v>13.1094</v>
@@ -844,13 +844,13 @@
         <v>36.8721</v>
       </c>
       <c r="S5" t="n">
-        <v>4.2323</v>
+        <v>1.3746</v>
       </c>
       <c r="T5" t="n">
-        <v>4.289400000000001</v>
+        <v>0.9307</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.05700000000000031</v>
+        <v>0.4437999999999998</v>
       </c>
       <c r="V5" t="n">
         <v>3.3339</v>
@@ -877,13 +877,13 @@
         <v>24</v>
       </c>
       <c r="D6" t="n">
-        <v>13.4234</v>
+        <v>6.8287</v>
       </c>
       <c r="E6" t="n">
-        <v>8.769600000000001</v>
+        <v>1.277900000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>4.654</v>
+        <v>5.5509</v>
       </c>
       <c r="G6" t="n">
         <v>5.923299999999999</v>
@@ -922,13 +922,13 @@
         <v>36.1307</v>
       </c>
       <c r="S6" t="n">
-        <v>17.6791</v>
+        <v>11.0842</v>
       </c>
       <c r="T6" t="n">
-        <v>13.3686</v>
+        <v>5.8768</v>
       </c>
       <c r="U6" t="n">
-        <v>4.3106</v>
+        <v>5.207400000000001</v>
       </c>
       <c r="V6" t="n">
         <v>-12.4025</v>
@@ -955,13 +955,13 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.3783</v>
+        <v>-1.1573</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9515</v>
+        <v>-0.8534999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4268999999999999</v>
+        <v>-0.3038</v>
       </c>
       <c r="G7" t="n">
         <v>-1.688</v>
@@ -1000,13 +1000,13 @@
         <v>0.7412</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4315</v>
+        <v>-0.2104</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.383</v>
+        <v>-0.285</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0485</v>
+        <v>0.0746</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. VIOQUE LOMBARDO</t>
+          <t>P. SECO LOPEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.370900000000001</v>
+        <v>-1.338099999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-17.4271</v>
+        <v>-4.641</v>
       </c>
       <c r="F8" t="n">
-        <v>12.0562</v>
+        <v>3.3033</v>
       </c>
       <c r="G8" t="n">
-        <v>-12.3904</v>
+        <v>11.6974</v>
       </c>
       <c r="H8" t="n">
-        <v>-10.2048</v>
+        <v>22.9611</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.1858</v>
+        <v>-11.2637</v>
       </c>
       <c r="J8" t="n">
-        <v>1.6165</v>
+        <v>31.7282</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.0826</v>
+        <v>31.2531</v>
       </c>
       <c r="L8" t="n">
-        <v>4.6986</v>
+        <v>0.4759000000000002</v>
       </c>
       <c r="M8" t="n">
-        <v>-14.0068</v>
+        <v>-20.0311</v>
       </c>
       <c r="N8" t="n">
-        <v>-7.1223</v>
+        <v>-8.291699999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>-6.8843</v>
+        <v>-11.7397</v>
       </c>
       <c r="P8" t="n">
-        <v>12.5994</v>
+        <v>-13.8964</v>
       </c>
       <c r="Q8" t="n">
-        <v>-30.2014</v>
+        <v>-49.8421</v>
       </c>
       <c r="R8" t="n">
-        <v>42.8015</v>
+        <v>35.9459</v>
       </c>
       <c r="S8" t="n">
-        <v>6.5027</v>
+        <v>-0.4572999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7763000000000002</v>
+        <v>-0.3672</v>
       </c>
       <c r="U8" t="n">
-        <v>5.7262</v>
+        <v>-0.08979999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>-12.0826</v>
+        <v>1.3177</v>
       </c>
       <c r="W8" t="n">
-        <v>10.382</v>
+        <v>13.8393</v>
       </c>
       <c r="X8" t="n">
-        <v>-22.4647</v>
+        <v>-12.5216</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. SECO LOPEZ</t>
+          <t>I. VIOQUE LOMBARDO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,70 +1108,70 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.814899999999999</v>
+        <v>-4.7036</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.537100000000001</v>
+        <v>-16.7359</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.277300000000001</v>
+        <v>12.0323</v>
       </c>
       <c r="G9" t="n">
-        <v>11.6974</v>
+        <v>-12.3904</v>
       </c>
       <c r="H9" t="n">
-        <v>22.9611</v>
+        <v>-10.2048</v>
       </c>
       <c r="I9" t="n">
-        <v>-11.2637</v>
+        <v>-2.1858</v>
       </c>
       <c r="J9" t="n">
-        <v>31.7282</v>
+        <v>1.6165</v>
       </c>
       <c r="K9" t="n">
-        <v>31.2531</v>
+        <v>-3.0826</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4759000000000002</v>
+        <v>4.6986</v>
       </c>
       <c r="M9" t="n">
-        <v>-20.0311</v>
+        <v>-14.0068</v>
       </c>
       <c r="N9" t="n">
-        <v>-8.291699999999999</v>
+        <v>-7.1223</v>
       </c>
       <c r="O9" t="n">
-        <v>-11.7397</v>
+        <v>-6.8843</v>
       </c>
       <c r="P9" t="n">
-        <v>-13.8964</v>
+        <v>12.5994</v>
       </c>
       <c r="Q9" t="n">
-        <v>-49.8421</v>
+        <v>-30.2014</v>
       </c>
       <c r="R9" t="n">
-        <v>35.9459</v>
+        <v>42.8015</v>
       </c>
       <c r="S9" t="n">
-        <v>-4.9335</v>
+        <v>7.1698</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2631000000000002</v>
+        <v>1.4677</v>
       </c>
       <c r="U9" t="n">
-        <v>-4.6701</v>
+        <v>5.7024</v>
       </c>
       <c r="V9" t="n">
-        <v>1.3177</v>
+        <v>-12.0826</v>
       </c>
       <c r="W9" t="n">
-        <v>13.8393</v>
+        <v>10.382</v>
       </c>
       <c r="X9" t="n">
-        <v>-12.5216</v>
+        <v>-22.4647</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>-16.425</v>
+        <v>-15.2178</v>
       </c>
       <c r="E10" t="n">
-        <v>-9.8901</v>
+        <v>-9.4437</v>
       </c>
       <c r="F10" t="n">
-        <v>-6.535</v>
+        <v>-5.7738</v>
       </c>
       <c r="G10" t="n">
         <v>-11.5227</v>
@@ -1234,13 +1234,13 @@
         <v>7.5966</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.5133</v>
+        <v>-0.3059999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8815999999999999</v>
+        <v>-0.4350999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6317999999999999</v>
+        <v>0.1294</v>
       </c>
       <c r="V10" t="n">
         <v>-6.1684</v>
@@ -1267,13 +1267,13 @@
         <v>23</v>
       </c>
       <c r="D11" t="n">
-        <v>-19.9744</v>
+        <v>-15.8605</v>
       </c>
       <c r="E11" t="n">
-        <v>-18.6653</v>
+        <v>-17.9773</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3088</v>
+        <v>2.1167</v>
       </c>
       <c r="G11" t="n">
         <v>-17.8505</v>
@@ -1312,13 +1312,13 @@
         <v>21.1226</v>
       </c>
       <c r="S11" t="n">
-        <v>-3.3086</v>
+        <v>0.8050000000000002</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1749</v>
+        <v>0.5134000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>-3.1334</v>
+        <v>0.2919999999999999</v>
       </c>
       <c r="V11" t="n">
         <v>-2.8917</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. DOBLADO GARCIA</t>
+          <t>P. CORREA GALLARDO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>-23.282</v>
+        <v>-17.5649</v>
       </c>
       <c r="E12" t="n">
-        <v>-25.2011</v>
+        <v>-12.4252</v>
       </c>
       <c r="F12" t="n">
-        <v>1.919400000000001</v>
+        <v>-5.139500000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>-28.3492</v>
+        <v>-20.3723</v>
       </c>
       <c r="H12" t="n">
-        <v>2.4361</v>
+        <v>-7.4416</v>
       </c>
       <c r="I12" t="n">
-        <v>-30.7853</v>
+        <v>-12.9306</v>
       </c>
       <c r="J12" t="n">
-        <v>-16.3412</v>
+        <v>-6.047999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>8.1511</v>
+        <v>2.3915</v>
       </c>
       <c r="L12" t="n">
-        <v>-24.4924</v>
+        <v>-8.4396</v>
       </c>
       <c r="M12" t="n">
-        <v>-12.0081</v>
+        <v>-14.3242</v>
       </c>
       <c r="N12" t="n">
-        <v>-5.715100000000001</v>
+        <v>-9.833</v>
       </c>
       <c r="O12" t="n">
-        <v>-6.2934</v>
+        <v>-4.491099999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>-9.0791</v>
+        <v>12.0436</v>
       </c>
       <c r="Q12" t="n">
-        <v>-56.5125</v>
+        <v>-4.8174</v>
       </c>
       <c r="R12" t="n">
-        <v>47.43369999999999</v>
+        <v>16.8612</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9012000000000002</v>
+        <v>-4.3912</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1749</v>
+        <v>-2.818</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7264000000000003</v>
+        <v>-1.5734</v>
       </c>
       <c r="V12" t="n">
-        <v>15.0472</v>
+        <v>-4.8448</v>
       </c>
       <c r="W12" t="n">
-        <v>47.827</v>
+        <v>1.2583</v>
       </c>
       <c r="X12" t="n">
-        <v>-32.7796</v>
+        <v>-6.1031</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. CORREA GALLARDO</t>
+          <t>A. DOBLADO GARCIA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D13" t="n">
-        <v>-23.8021</v>
+        <v>-17.9068</v>
       </c>
       <c r="E13" t="n">
-        <v>-16.7685</v>
+        <v>-23.0502</v>
       </c>
       <c r="F13" t="n">
-        <v>-7.0333</v>
+        <v>5.143199999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>-20.3723</v>
+        <v>-28.3492</v>
       </c>
       <c r="H13" t="n">
-        <v>-7.4416</v>
+        <v>2.4361</v>
       </c>
       <c r="I13" t="n">
-        <v>-12.9306</v>
+        <v>-30.7853</v>
       </c>
       <c r="J13" t="n">
-        <v>-6.047999999999999</v>
+        <v>-16.3412</v>
       </c>
       <c r="K13" t="n">
-        <v>2.3915</v>
+        <v>8.1511</v>
       </c>
       <c r="L13" t="n">
-        <v>-8.4396</v>
+        <v>-24.4924</v>
       </c>
       <c r="M13" t="n">
-        <v>-14.3242</v>
+        <v>-12.0081</v>
       </c>
       <c r="N13" t="n">
-        <v>-9.833</v>
+        <v>-5.715100000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>-4.491099999999999</v>
+        <v>-6.2934</v>
       </c>
       <c r="P13" t="n">
-        <v>12.0436</v>
+        <v>-9.0791</v>
       </c>
       <c r="Q13" t="n">
-        <v>-4.8174</v>
+        <v>-56.5125</v>
       </c>
       <c r="R13" t="n">
-        <v>16.8612</v>
+        <v>47.43369999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>-10.6284</v>
+        <v>4.4739</v>
       </c>
       <c r="T13" t="n">
-        <v>-7.1613</v>
+        <v>1.9767</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.4669</v>
+        <v>2.4976</v>
       </c>
       <c r="V13" t="n">
-        <v>-4.8448</v>
+        <v>15.0472</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2583</v>
+        <v>47.827</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.1031</v>
+        <v>-32.7796</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>17</v>
       </c>
       <c r="D14" t="n">
-        <v>-29.7859</v>
+        <v>-27.2817</v>
       </c>
       <c r="E14" t="n">
-        <v>-22.6016</v>
+        <v>-21.0231</v>
       </c>
       <c r="F14" t="n">
-        <v>-7.1843</v>
+        <v>-6.2582</v>
       </c>
       <c r="G14" t="n">
         <v>-23.5655</v>
@@ -1546,13 +1546,13 @@
         <v>12.9701</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.3669</v>
+        <v>-0.8626</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.3786</v>
+        <v>-0.8002000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.9882</v>
+        <v>-0.06200000000000003</v>
       </c>
       <c r="V14" t="n">
         <v>-0.6300999999999999</v>
@@ -1579,13 +1579,13 @@
         <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>-44.7024</v>
+        <v>-43.1144</v>
       </c>
       <c r="E15" t="n">
-        <v>-70.63930000000001</v>
+        <v>-66.434</v>
       </c>
       <c r="F15" t="n">
-        <v>25.9363</v>
+        <v>23.3196</v>
       </c>
       <c r="G15" t="n">
         <v>-33.3458</v>
@@ -1624,13 +1624,13 @@
         <v>42.2454</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7960000000000003</v>
+        <v>2.3846</v>
       </c>
       <c r="T15" t="n">
-        <v>-6.175</v>
+        <v>-1.9697</v>
       </c>
       <c r="U15" t="n">
-        <v>6.970800000000001</v>
+        <v>4.3543</v>
       </c>
       <c r="V15" t="n">
         <v>10.6377</v>
@@ -1657,19 +1657,19 @@
         <v>26</v>
       </c>
       <c r="D16" t="n">
-        <v>-25.61540000000001</v>
+        <v>-2.603300000000004</v>
       </c>
       <c r="E16" t="n">
-        <v>-97.08080000000001</v>
+        <v>-87.7796</v>
       </c>
       <c r="F16" t="n">
-        <v>71.4659</v>
+        <v>85.17689999999999</v>
       </c>
       <c r="G16" t="n">
         <v>-81.53130000000002</v>
       </c>
       <c r="H16" t="n">
-        <v>16.6526</v>
+        <v>16.65259999999999</v>
       </c>
       <c r="I16" t="n">
         <v>-98.18470000000001</v>
@@ -1681,7 +1681,7 @@
         <v>112.3082</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.534199999999999</v>
+        <v>-1.534199999999998</v>
       </c>
       <c r="M16" t="n">
         <v>-192.3039</v>
@@ -1693,7 +1693,7 @@
         <v>-96.65090000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>16.6754</v>
+        <v>16.67539999999999</v>
       </c>
       <c r="Q16" t="n">
         <v>-393.7333</v>
@@ -1702,13 +1702,13 @@
         <v>410.411</v>
       </c>
       <c r="S16" t="n">
-        <v>13.4363</v>
+        <v>36.4471</v>
       </c>
       <c r="T16" t="n">
-        <v>-3.196899999999997</v>
+        <v>6.1049</v>
       </c>
       <c r="U16" t="n">
-        <v>16.6339</v>
+        <v>30.3442</v>
       </c>
       <c r="V16" t="n">
         <v>25.80349999999999</v>
